--- a/maps/map1.xlsx
+++ b/maps/map1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\projects in programming\python\AgentStorage\AgentStorageDiplom\maps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{555E3E26-6163-4D27-B5A8-D7F8C5DE956A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C37868-B1D3-440A-B28B-F83E5816AC88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="map1" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="254">
   <si>
     <t>W|-----|-----|{}</t>
   </si>
@@ -2394,7 +2394,9 @@
       <c r="D15" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="7"/>
+      <c r="E15" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="F15" s="7" t="s">
         <v>34</v>
       </c>
@@ -2480,7 +2482,9 @@
       <c r="D16" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="E16" s="7"/>
+      <c r="E16" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="F16" s="5" t="s">
         <v>42</v>
       </c>
@@ -2566,7 +2570,9 @@
       <c r="D17" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="E17" s="7"/>
+      <c r="E17" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="F17" s="5" t="s">
         <v>52</v>
       </c>
@@ -2658,7 +2664,9 @@
       <c r="D18" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="E18" s="7"/>
+      <c r="E18" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="F18" s="5" t="s">
         <v>62</v>
       </c>
@@ -2742,7 +2750,9 @@
       <c r="D19" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="E19" s="7"/>
+      <c r="E19" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="F19" s="5" t="s">
         <v>72</v>
       </c>
@@ -2826,7 +2836,9 @@
       <c r="D20" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="E20" s="7"/>
+      <c r="E20" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="F20" s="5" t="s">
         <v>82</v>
       </c>
@@ -2910,7 +2922,9 @@
       <c r="D21" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="E21" s="7"/>
+      <c r="E21" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="F21" s="5" t="s">
         <v>92</v>
       </c>
@@ -2994,7 +3008,9 @@
       <c r="D22" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="E22" s="7"/>
+      <c r="E22" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="F22" s="5" t="s">
         <v>102</v>
       </c>
@@ -3078,7 +3094,9 @@
       <c r="D23" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="E23" s="7"/>
+      <c r="E23" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="F23" s="5" t="s">
         <v>112</v>
       </c>
@@ -3162,7 +3180,9 @@
       <c r="D24" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="E24" s="7"/>
+      <c r="E24" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="F24" s="5" t="s">
         <v>122</v>
       </c>
@@ -3246,7 +3266,9 @@
       <c r="D25" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="E25" s="7"/>
+      <c r="E25" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="F25" s="7" t="s">
         <v>34</v>
       </c>
@@ -3259,7 +3281,9 @@
       <c r="I25" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="J25" s="7"/>
+      <c r="J25" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="K25" s="7" t="s">
         <v>34</v>
       </c>
@@ -3267,28 +3291,32 @@
         <v>34</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N25" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="P25" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q25" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="O25" s="7"/>
-      <c r="P25" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q25" s="7" t="s">
-        <v>34</v>
-      </c>
       <c r="R25" s="7" t="s">
         <v>34</v>
       </c>
       <c r="S25" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="T25" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="U25" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="T25" s="7"/>
-      <c r="U25" s="7" t="s">
-        <v>34</v>
-      </c>
       <c r="V25" s="7" t="s">
         <v>34</v>
       </c>
@@ -3296,7 +3324,7 @@
         <v>34</v>
       </c>
       <c r="X25" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Y25" s="7" t="s">
         <v>34</v>
@@ -3439,8 +3467,12 @@
       <c r="M27" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="N27" s="7"/>
-      <c r="O27" s="7"/>
+      <c r="N27" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="O27" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="P27" s="12" t="s">
         <v>244</v>
       </c>

--- a/maps/map1.xlsx
+++ b/maps/map1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\projects in programming\python\AgentStorage\AgentStorageDiplom\maps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C37868-B1D3-440A-B28B-F83E5816AC88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7492A0B1-B656-4CF1-A183-743C5571B13A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="map1" sheetId="3" r:id="rId1"/>
@@ -835,7 +835,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -896,6 +896,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -909,7 +915,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -927,6 +933,8 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2235,7 +2243,7 @@
       <c r="K13" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="7" t="s">
+      <c r="L13" s="17" t="s">
         <v>34</v>
       </c>
       <c r="M13" s="7" t="s">
@@ -2479,7 +2487,7 @@
       <c r="C16" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="18" t="s">
         <v>233</v>
       </c>
       <c r="E16" s="7" t="s">

--- a/maps/map1.xlsx
+++ b/maps/map1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\projects in programming\python\AgentStorage\AgentStorageDiplom\maps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7492A0B1-B656-4CF1-A183-743C5571B13A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C105D32F-44B3-4A60-A6FD-E187AD219726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -898,7 +898,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>

--- a/maps/map1.xlsx
+++ b/maps/map1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\projects in programming\python\AgentStorage\AgentStorageDiplom\maps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C105D32F-44B3-4A60-A6FD-E187AD219726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD351ED9-BFC0-48A6-81FE-5C98AA490620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,12 +23,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="254">
   <si>
-    <t>W|-----|-----|{}</t>
-  </si>
-  <si>
-    <t>E|-----|-----|{}</t>
-  </si>
-  <si>
     <t>P|---|---|{"packer_id":1}</t>
   </si>
   <si>
@@ -783,6 +777,12 @@
   </si>
   <si>
     <t>B|n-w-s-e|n-w-s-e|{"packer_id":2,"zone":"buffer","slot":11}</t>
+  </si>
+  <si>
+    <t>E|---|---|{}</t>
+  </si>
+  <si>
+    <t>W|---|---|{}</t>
   </si>
 </sst>
 </file>
@@ -1171,1034 +1171,1034 @@
   <sheetData>
     <row r="1" spans="1:39" ht="12.75">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" spans="1:39" ht="12.75">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="Y2" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="Z2" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3" spans="1:39" ht="12.75">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="R3" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="S3" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="T3" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="U3" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="V3" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="W3" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="X3" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="Y3" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="Z3" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:39" ht="12.75">
       <c r="A4" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F4" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H4" s="5" t="s">
+      <c r="K4" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="L4" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4" s="5" t="s">
+      <c r="M4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N4" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="K4" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="L4" s="5" t="s">
+      <c r="O4" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="P4" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="M4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="N4" s="5" t="s">
+      <c r="Q4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R4" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="O4" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="P4" s="5" t="s">
+      <c r="S4" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="T4" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="Q4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="R4" s="5" t="s">
+      <c r="U4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="V4" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="S4" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="T4" s="5" t="s">
+      <c r="W4" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="X4" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="U4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="V4" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="W4" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="X4" s="5" t="s">
-        <v>141</v>
-      </c>
       <c r="Y4" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Z4" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA4" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:39" ht="12.75">
       <c r="A5" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="5" t="s">
+      <c r="I5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="G5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="K5" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="I5" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" s="5" t="s">
+      <c r="M5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N5" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="K5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="L5" s="5" t="s">
+      <c r="O5" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="P5" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="M5" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="N5" s="5" t="s">
+      <c r="Q5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R5" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="O5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="P5" s="5" t="s">
+      <c r="S5" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="T5" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="Q5" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="R5" s="5" t="s">
+      <c r="U5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="V5" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="S5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="T5" s="5" t="s">
+      <c r="W5" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="X5" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="U5" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="V5" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="W5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="X5" s="5" t="s">
-        <v>152</v>
-      </c>
       <c r="Y5" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Z5" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA5" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:39" ht="12.75">
       <c r="A6" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="5" t="s">
+      <c r="I6" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="G6" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" s="5" t="s">
+      <c r="K6" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="L6" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="I6" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J6" s="5" t="s">
+      <c r="M6" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N6" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="K6" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="L6" s="5" t="s">
+      <c r="O6" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="P6" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="M6" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="N6" s="5" t="s">
+      <c r="Q6" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R6" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="O6" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="P6" s="5" t="s">
+      <c r="S6" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="T6" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="Q6" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="R6" s="5" t="s">
+      <c r="U6" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="V6" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="S6" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="T6" s="5" t="s">
+      <c r="W6" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="X6" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="U6" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="V6" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="W6" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="X6" s="5" t="s">
-        <v>163</v>
-      </c>
       <c r="Y6" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Z6" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA6" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7" spans="1:39" ht="12.75">
       <c r="A7" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D7" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="5" t="s">
+      <c r="I7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="G7" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="K7" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="L7" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="I7" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J7" s="5" t="s">
+      <c r="M7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N7" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="K7" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="L7" s="5" t="s">
+      <c r="O7" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="P7" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="M7" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="N7" s="5" t="s">
+      <c r="Q7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R7" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="O7" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="P7" s="5" t="s">
+      <c r="S7" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="T7" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="Q7" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="R7" s="5" t="s">
+      <c r="U7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="V7" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="S7" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="T7" s="5" t="s">
+      <c r="W7" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="X7" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="U7" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="V7" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="W7" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="X7" s="5" t="s">
-        <v>174</v>
-      </c>
       <c r="Y7" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Z7" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA7" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="8" spans="1:39" ht="12.75">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D8" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="5" t="s">
+      <c r="I8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="G8" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="5" t="s">
+      <c r="K8" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="L8" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J8" s="5" t="s">
+      <c r="M8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N8" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="K8" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="L8" s="5" t="s">
+      <c r="O8" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="P8" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="M8" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="N8" s="5" t="s">
+      <c r="Q8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R8" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="O8" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="P8" s="5" t="s">
+      <c r="S8" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="T8" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="Q8" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="R8" s="5" t="s">
+      <c r="U8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="V8" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="S8" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="T8" s="5" t="s">
+      <c r="W8" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="X8" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="U8" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="V8" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="W8" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="X8" s="5" t="s">
-        <v>185</v>
-      </c>
       <c r="Y8" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Z8" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA8" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="9" spans="1:39" ht="12.75">
       <c r="A9" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D9" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H9" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="5" t="s">
+      <c r="I9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="G9" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="5" t="s">
+      <c r="K9" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="L9" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="I9" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J9" s="5" t="s">
+      <c r="M9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N9" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="K9" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="L9" s="5" t="s">
+      <c r="O9" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="P9" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="M9" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="N9" s="5" t="s">
+      <c r="Q9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R9" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="O9" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="P9" s="5" t="s">
+      <c r="S9" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="T9" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="Q9" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="R9" s="5" t="s">
+      <c r="U9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="V9" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="S9" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="T9" s="5" t="s">
+      <c r="W9" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="X9" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="U9" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="V9" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="W9" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="X9" s="5" t="s">
-        <v>196</v>
-      </c>
       <c r="Y9" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Z9" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA9" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AB9" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10" spans="1:39" ht="12.75">
       <c r="A10" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D10" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="5" t="s">
+      <c r="I10" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J10" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="G10" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="5" t="s">
+      <c r="K10" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="L10" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="I10" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J10" s="5" t="s">
+      <c r="M10" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N10" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="K10" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="L10" s="5" t="s">
+      <c r="O10" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="P10" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="M10" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="N10" s="5" t="s">
+      <c r="Q10" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R10" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="O10" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="P10" s="5" t="s">
+      <c r="S10" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="T10" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="Q10" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="R10" s="5" t="s">
+      <c r="U10" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="V10" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="S10" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="T10" s="5" t="s">
+      <c r="W10" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="X10" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="U10" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="V10" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="W10" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="X10" s="5" t="s">
-        <v>207</v>
-      </c>
       <c r="Y10" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Z10" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA10" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AB10" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11" spans="1:39" ht="12.75">
       <c r="A11" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D11" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H11" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="5" t="s">
+      <c r="I11" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J11" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="G11" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" s="5" t="s">
+      <c r="K11" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="L11" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="I11" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J11" s="5" t="s">
+      <c r="M11" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N11" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="K11" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="L11" s="5" t="s">
+      <c r="O11" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="P11" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="M11" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="N11" s="5" t="s">
+      <c r="Q11" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R11" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="O11" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="P11" s="5" t="s">
+      <c r="S11" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="T11" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="Q11" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="R11" s="5" t="s">
+      <c r="U11" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="V11" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="S11" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="T11" s="5" t="s">
+      <c r="W11" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="X11" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="U11" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="V11" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="W11" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="X11" s="5" t="s">
-        <v>218</v>
-      </c>
       <c r="Y11" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA11" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AB11" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12" spans="1:39" ht="12.75">
       <c r="A12" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D12" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H12" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" s="5" t="s">
+      <c r="I12" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J12" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="G12" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H12" s="5" t="s">
+      <c r="K12" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="L12" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="I12" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J12" s="5" t="s">
+      <c r="M12" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N12" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="K12" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="L12" s="5" t="s">
+      <c r="O12" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="P12" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="M12" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="N12" s="5" t="s">
+      <c r="Q12" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R12" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="O12" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="P12" s="5" t="s">
+      <c r="S12" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="T12" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="Q12" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="R12" s="5" t="s">
+      <c r="U12" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="V12" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="S12" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="T12" s="5" t="s">
+      <c r="W12" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="X12" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="U12" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="V12" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="W12" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="X12" s="5" t="s">
-        <v>229</v>
-      </c>
       <c r="Y12" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Z12" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA12" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AB12" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
@@ -2211,88 +2211,88 @@
     </row>
     <row r="13" spans="1:39" ht="12.75">
       <c r="A13" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L13" s="17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="R13" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S13" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="T13" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="U13" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="V13" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="W13" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="X13" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y13" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Z13" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA13" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AB13" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
@@ -2301,88 +2301,88 @@
     </row>
     <row r="14" spans="1:39" ht="12.75">
       <c r="A14" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R14" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S14" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="T14" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="U14" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="V14" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="W14" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="X14" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y14" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z14" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA14" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AB14" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="AD14" s="8"/>
       <c r="AE14" s="4"/>
@@ -2391,264 +2391,264 @@
     </row>
     <row r="15" spans="1:39" ht="12.75">
       <c r="A15" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="H15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="L15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="O15" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H15" s="7" t="s">
+      <c r="P15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="R15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="S15" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="T15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="U15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="V15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="W15" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="J15" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="L15" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M15" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="N15" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="O15" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="P15" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q15" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="R15" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="S15" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="T15" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="U15" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="V15" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="W15" s="7" t="s">
-        <v>36</v>
-      </c>
       <c r="X15" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y15" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z15" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA15" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AB15" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="AL15" s="9"/>
       <c r="AM15" s="9"/>
     </row>
     <row r="16" spans="1:39" ht="12.75">
       <c r="A16" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F16" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J16" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G16" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="H16" s="5" t="s">
+      <c r="K16" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="L16" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="I16" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J16" s="5" t="s">
+      <c r="M16" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N16" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="K16" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="L16" s="5" t="s">
+      <c r="O16" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="P16" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="M16" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="N16" s="5" t="s">
+      <c r="Q16" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R16" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="O16" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="P16" s="5" t="s">
+      <c r="S16" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="T16" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="Q16" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="R16" s="5" t="s">
+      <c r="U16" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="V16" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="S16" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="T16" s="5" t="s">
+      <c r="W16" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="X16" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="U16" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="V16" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="W16" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="X16" s="5" t="s">
-        <v>51</v>
-      </c>
       <c r="Y16" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Z16" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA16" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AB16" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="AL16" s="9"/>
       <c r="AM16" s="9"/>
     </row>
     <row r="17" spans="1:39" ht="12.75">
       <c r="A17" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F17" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J17" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="G17" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H17" s="5" t="s">
+      <c r="K17" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="L17" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="I17" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J17" s="5" t="s">
+      <c r="M17" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N17" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="K17" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="L17" s="5" t="s">
+      <c r="O17" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="P17" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="M17" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="N17" s="5" t="s">
+      <c r="Q17" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R17" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="O17" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="P17" s="5" t="s">
+      <c r="S17" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="T17" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="Q17" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="R17" s="5" t="s">
+      <c r="U17" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="V17" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="S17" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="T17" s="5" t="s">
+      <c r="W17" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="X17" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="U17" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="V17" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="W17" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="X17" s="5" t="s">
-        <v>61</v>
-      </c>
       <c r="Y17" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Z17" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA17" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AB17" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="AF17" s="4"/>
       <c r="AG17" s="4"/>
@@ -2661,1209 +2661,1209 @@
     </row>
     <row r="18" spans="1:39" ht="12.75">
       <c r="A18" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F18" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J18" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G18" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H18" s="5" t="s">
+      <c r="K18" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="L18" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="I18" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J18" s="5" t="s">
+      <c r="M18" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N18" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="K18" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="L18" s="5" t="s">
+      <c r="O18" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="P18" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="M18" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="N18" s="5" t="s">
+      <c r="Q18" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R18" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="O18" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="P18" s="5" t="s">
+      <c r="S18" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="T18" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="Q18" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="R18" s="5" t="s">
+      <c r="U18" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="V18" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="S18" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="T18" s="5" t="s">
+      <c r="W18" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="X18" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="U18" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="V18" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="W18" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="X18" s="5" t="s">
-        <v>71</v>
-      </c>
       <c r="Y18" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Z18" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA18" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AB18" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="19" spans="1:39" ht="12.75">
       <c r="A19" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F19" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J19" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="G19" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H19" s="5" t="s">
+      <c r="K19" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="L19" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="I19" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J19" s="5" t="s">
+      <c r="M19" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N19" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="K19" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="L19" s="5" t="s">
+      <c r="O19" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="P19" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="M19" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="N19" s="5" t="s">
+      <c r="Q19" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R19" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="O19" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="P19" s="5" t="s">
+      <c r="S19" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="T19" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="Q19" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="R19" s="5" t="s">
+      <c r="U19" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="V19" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="S19" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="T19" s="5" t="s">
+      <c r="W19" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="X19" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="U19" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="V19" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="W19" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="X19" s="5" t="s">
-        <v>81</v>
-      </c>
       <c r="Y19" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Z19" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA19" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AB19" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="20" spans="1:39" ht="12.75">
       <c r="A20" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F20" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J20" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="G20" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H20" s="5" t="s">
+      <c r="K20" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="L20" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="I20" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J20" s="5" t="s">
+      <c r="M20" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N20" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="K20" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="L20" s="5" t="s">
+      <c r="O20" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="P20" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="M20" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="N20" s="5" t="s">
+      <c r="Q20" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R20" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="O20" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="P20" s="5" t="s">
+      <c r="S20" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="T20" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="Q20" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="R20" s="5" t="s">
+      <c r="U20" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="V20" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="S20" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="T20" s="5" t="s">
+      <c r="W20" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="X20" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="U20" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="V20" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="W20" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="X20" s="5" t="s">
-        <v>91</v>
-      </c>
       <c r="Y20" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Z20" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA20" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AB20" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="21" spans="1:39" ht="12.75">
       <c r="A21" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F21" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J21" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="G21" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H21" s="5" t="s">
+      <c r="K21" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="L21" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="I21" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J21" s="5" t="s">
+      <c r="M21" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N21" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="K21" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="L21" s="5" t="s">
+      <c r="O21" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="P21" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="M21" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="N21" s="5" t="s">
+      <c r="Q21" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R21" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="O21" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="P21" s="5" t="s">
+      <c r="S21" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="T21" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="Q21" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="R21" s="5" t="s">
+      <c r="U21" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="V21" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="S21" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="T21" s="5" t="s">
+      <c r="W21" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="X21" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="U21" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="V21" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="W21" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="X21" s="5" t="s">
-        <v>101</v>
-      </c>
       <c r="Y21" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Z21" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA21" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AB21" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="22" spans="1:39" ht="12.75">
       <c r="A22" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F22" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J22" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="G22" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H22" s="5" t="s">
+      <c r="K22" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="L22" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="I22" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J22" s="5" t="s">
+      <c r="M22" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N22" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="K22" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="L22" s="5" t="s">
+      <c r="O22" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="P22" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="M22" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="N22" s="5" t="s">
+      <c r="Q22" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R22" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="O22" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="P22" s="5" t="s">
+      <c r="S22" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="T22" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="Q22" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="R22" s="5" t="s">
+      <c r="U22" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="V22" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="S22" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="T22" s="5" t="s">
+      <c r="W22" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="X22" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="U22" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="V22" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="W22" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="X22" s="5" t="s">
-        <v>111</v>
-      </c>
       <c r="Y22" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Z22" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA22" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AB22" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="23" spans="1:39" ht="12.75">
       <c r="A23" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F23" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J23" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="G23" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H23" s="5" t="s">
+      <c r="K23" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="L23" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="I23" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J23" s="5" t="s">
+      <c r="M23" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N23" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="K23" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="L23" s="5" t="s">
+      <c r="O23" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="P23" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="M23" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="N23" s="5" t="s">
+      <c r="Q23" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R23" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="O23" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="P23" s="5" t="s">
+      <c r="S23" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="T23" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="Q23" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="R23" s="5" t="s">
+      <c r="U23" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="V23" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="S23" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="T23" s="5" t="s">
+      <c r="W23" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="X23" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="U23" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="V23" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="W23" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="X23" s="5" t="s">
-        <v>121</v>
-      </c>
       <c r="Y23" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Z23" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA23" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AB23" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="24" spans="1:39" ht="12.75">
       <c r="A24" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F24" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J24" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="G24" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H24" s="5" t="s">
+      <c r="K24" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="L24" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="I24" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J24" s="5" t="s">
+      <c r="M24" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="N24" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="K24" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="L24" s="5" t="s">
+      <c r="O24" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="P24" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="M24" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="N24" s="5" t="s">
+      <c r="Q24" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R24" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="O24" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="P24" s="5" t="s">
+      <c r="S24" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="T24" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="Q24" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="R24" s="5" t="s">
+      <c r="U24" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="V24" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="S24" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="T24" s="5" t="s">
+      <c r="W24" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="X24" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="U24" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="V24" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="W24" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="X24" s="5" t="s">
-        <v>131</v>
-      </c>
       <c r="Y24" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Z24" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA24" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AB24" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="25" spans="1:39" ht="12.75">
       <c r="A25" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="C25" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D25" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>35</v>
-      </c>
       <c r="J25" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P25" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q25" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="R25" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S25" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="T25" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="U25" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="V25" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="W25" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="X25" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y25" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z25" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA25" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AB25" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="AD25" s="4"/>
     </row>
     <row r="26" spans="1:39" ht="12.75">
       <c r="A26" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N26" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="O26" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P26" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q26" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R26" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S26" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="T26" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="U26" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="V26" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="W26" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="X26" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y26" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z26" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA26" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AB26" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="AD26" s="4"/>
     </row>
     <row r="27" spans="1:39" ht="12.75">
       <c r="A27" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D27" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="F27" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="E27" s="12" t="s">
+      <c r="G27" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="F27" s="12" t="s">
+      <c r="H27" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="G27" s="12" t="s">
+      <c r="I27" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="H27" s="12" t="s">
+      <c r="J27" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="I27" s="12" t="s">
+      <c r="K27" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="J27" s="12" t="s">
+      <c r="L27" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="K27" s="12" t="s">
+      <c r="M27" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="L27" s="12" t="s">
+      <c r="N27" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="O27" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="P27" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="M27" s="12" t="s">
+      <c r="Q27" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="N27" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="O27" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="P27" s="12" t="s">
+      <c r="R27" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="Q27" s="12" t="s">
+      <c r="S27" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="R27" s="12" t="s">
+      <c r="T27" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="S27" s="12" t="s">
+      <c r="U27" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="T27" s="12" t="s">
+      <c r="V27" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="U27" s="12" t="s">
+      <c r="W27" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="V27" s="12" t="s">
+      <c r="X27" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="W27" s="12" t="s">
+      <c r="Y27" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="X27" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="Y27" s="12" t="s">
-        <v>253</v>
-      </c>
       <c r="Z27" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA27" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AB27" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="AD27" s="4"/>
     </row>
     <row r="28" spans="1:39" ht="12.75">
       <c r="A28" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="C28" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="N28" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="O28" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E28" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="I28" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="K28" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L28" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M28" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="N28" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="O28" s="7" t="s">
-        <v>36</v>
-      </c>
       <c r="P28" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q28" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R28" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S28" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="T28" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="U28" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="V28" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="W28" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="X28" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y28" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z28" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA28" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AB28" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="29" spans="1:39" ht="15.75" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D29" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="G29" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="H29" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="G29" s="14" t="s">
+      <c r="I29" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="H29" s="14" t="s">
+      <c r="J29" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="I29" s="14" t="s">
+      <c r="K29" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="J29" s="14" t="s">
+      <c r="L29" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="K29" s="14" t="s">
+      <c r="M29" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="L29" s="14" t="s">
+      <c r="N29" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="O29" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="P29" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="M29" s="14" t="s">
+      <c r="Q29" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="N29" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="O29" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="P29" s="13" t="s">
+      <c r="R29" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="Q29" s="13" t="s">
+      <c r="S29" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="R29" s="13" t="s">
+      <c r="T29" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="S29" s="13" t="s">
+      <c r="U29" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="T29" s="13" t="s">
+      <c r="V29" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="U29" s="13" t="s">
+      <c r="W29" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="V29" s="13" t="s">
+      <c r="X29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="W29" s="13" t="s">
+      <c r="Y29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="X29" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y29" s="13" t="s">
-        <v>23</v>
-      </c>
       <c r="Z29" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA29" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AB29" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="30" spans="1:39" ht="15.75" customHeight="1">
       <c r="A30" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="P30" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="M30" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="N30" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="O30" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="P30" s="11" t="s">
-        <v>3</v>
-      </c>
       <c r="Q30" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="T30" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="U30" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="V30" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="W30" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="X30" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="Y30" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="Z30" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AA30" s="3" t="s">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="AB30" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="31" spans="1:39" ht="15.75" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="V31" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="X31" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="Y31" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="Z31" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="AA31" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="AB31" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -3879,82 +3879,82 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/maps/map1.xlsx
+++ b/maps/map1.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\projects in programming\python\AgentStorage\AgentStorageDiplom\maps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD351ED9-BFC0-48A6-81FE-5C98AA490620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{046C11BC-2F5C-437B-B889-BB6256504238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="map1" sheetId="3" r:id="rId1"/>
+    <sheet name="map" sheetId="3" r:id="rId1"/>
     <sheet name="Лист1" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
@@ -21,768 +21,705 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="233">
   <si>
     <t>P|---|---|{"packer_id":1}</t>
   </si>
   <si>
+    <t>Z|n-w-s-e|---|{"packer_id":1,"zone":"order","slot":10}</t>
+  </si>
+  <si>
+    <t>Z|n-w-s-e|---|{"packer_id":1,"zone":"order","slot":9}</t>
+  </si>
+  <si>
+    <t>Z|n-w-s-e|---|{"packer_id":1,"zone":"order","slot":8}</t>
+  </si>
+  <si>
+    <t>Z|n-w-s-e|---|{"packer_id":1,"zone":"order","slot":7}</t>
+  </si>
+  <si>
+    <t>Z|n-w-s-e|---|{"packer_id":1,"zone":"order","slot":6}</t>
+  </si>
+  <si>
+    <t>Z|n-w-s-e|---|{"packer_id":1,"zone":"order","slot":5}</t>
+  </si>
+  <si>
+    <t>Z|n-w-s-e|---|{"packer_id":1,"zone":"order","slot":4}</t>
+  </si>
+  <si>
+    <t>Z|n-w-s-e|---|{"packer_id":1,"zone":"order","slot":3}</t>
+  </si>
+  <si>
+    <t>Z|n-w-s-e|---|{"packer_id":1,"zone":"order","slot":2}</t>
+  </si>
+  <si>
+    <t>Z|n-w-s-e|---|{"packer_id":1,"zone":"order","slot":1}</t>
+  </si>
+  <si>
+    <t>Z|n-w-s-e|---|{"packer_id":2,"zone":"order","slot":1}</t>
+  </si>
+  <si>
+    <t>Z|n-w-s-e|---|{"packer_id":2,"zone":"order","slot":2}</t>
+  </si>
+  <si>
+    <t>Z|n-w-s-e|---|{"packer_id":2,"zone":"order","slot":3}</t>
+  </si>
+  <si>
+    <t>Z|n-w-s-e|---|{"packer_id":2,"zone":"order","slot":4}</t>
+  </si>
+  <si>
+    <t>Z|n-w-s-e|---|{"packer_id":2,"zone":"order","slot":5}</t>
+  </si>
+  <si>
+    <t>Z|n-w-s-e|---|{"packer_id":2,"zone":"order","slot":6}</t>
+  </si>
+  <si>
+    <t>Z|n-w-s-e|---|{"packer_id":2,"zone":"order","slot":7}</t>
+  </si>
+  <si>
+    <t>Z|n-w-s-e|---|{"packer_id":2,"zone":"order","slot":8}</t>
+  </si>
+  <si>
+    <t>Z|n-w-s-e|---|{"packer_id":2,"zone":"order","slot":9}</t>
+  </si>
+  <si>
+    <t>Z|n-w-s-e|---|{"packer_id":2,"zone":"order","slot":10}</t>
+  </si>
+  <si>
+    <t>F|n-w-s-e|n-w-s-e|{}</t>
+  </si>
+  <si>
+    <t>F|-w-s-e|-w-s-e|{}</t>
+  </si>
+  <si>
+    <t>F|n-w--e|n-w--e|{}</t>
+  </si>
+  <si>
+    <t>F|n--s-e|n--s-e|{}</t>
+  </si>
+  <si>
+    <t>F|n---e|n---e|{}</t>
+  </si>
+  <si>
+    <t>F|--s-|-w-s-e|{}</t>
+  </si>
+  <si>
+    <t>F|n---|-w-s-e|{}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":0}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":99}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":108}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":117}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":126}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":135}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":144}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":153}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":162}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":171}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":180}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":100}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":109}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":118}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":127}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":136}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":145}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":154}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":163}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":172}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":181}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":101}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":110}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":119}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":128}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":137}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":146}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":155}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":164}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":173}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":182}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":102}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":111}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":120}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":129}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":138}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":147}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":156}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":165}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":174}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":183}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":103}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":112}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":121}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":130}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":139}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":148}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":157}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":166}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":175}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":184}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":104}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":113}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":122}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":131}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":140}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":149}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":158}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":167}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":176}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":185}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":105}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":114}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":123}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":132}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":141}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":150}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":159}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":168}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":177}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":186}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":106}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":115}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":124}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":133}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":142}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":151}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":160}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":169}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":178}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":187}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":107}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":116}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":125}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":134}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":143}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":152}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":161}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":170}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":179}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":188}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":9}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":18}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":27}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":36}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":45}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":54}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":63}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":72}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":81}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":90}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":1}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":10}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":19}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":28}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":37}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":46}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":55}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":64}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":73}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":82}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":91}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":2}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":11}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":20}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":29}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":38}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":47}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":56}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":65}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":74}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":83}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":92}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":3}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":12}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":21}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":30}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":39}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":48}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":57}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":66}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":75}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":84}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":93}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":4}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":13}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":22}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":31}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":40}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":49}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":58}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":67}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":76}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":85}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":94}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":5}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":14}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":23}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":32}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":41}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":50}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":59}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":68}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":77}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":86}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":95}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":6}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":15}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":24}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":33}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":42}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":51}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":60}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":69}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":78}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":87}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":96}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":7}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":16}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":25}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":34}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":43}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":52}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":61}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":70}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":79}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":88}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":97}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":8}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":17}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":26}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":35}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":44}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":53}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":62}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":71}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":80}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":89}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":98}</t>
+  </si>
+  <si>
+    <t>вниз</t>
+  </si>
+  <si>
+    <t>вверх</t>
+  </si>
+  <si>
+    <t>F|n---|n-w--e|{}</t>
+  </si>
+  <si>
+    <t>F|n--s-e|n-w-s-e|{}</t>
+  </si>
+  <si>
+    <t>E|---|---|{}</t>
+  </si>
+  <si>
+    <t>W|---|---|{}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":189}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":190}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":191}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":192}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":193}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":194}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":195}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":196}</t>
+  </si>
+  <si>
+    <t>S|-w--e|n-w-s-e|{"shelf_id":197}</t>
+  </si>
+  <si>
     <t>P|---|---|{"packer_id":2}</t>
-  </si>
-  <si>
-    <t>Z|n-w-s-e|---|{"packer_id":1,"zone":"order","slot":10}</t>
-  </si>
-  <si>
-    <t>Z|n-w-s-e|---|{"packer_id":1,"zone":"order","slot":9}</t>
-  </si>
-  <si>
-    <t>Z|n-w-s-e|---|{"packer_id":1,"zone":"order","slot":8}</t>
-  </si>
-  <si>
-    <t>Z|n-w-s-e|---|{"packer_id":1,"zone":"order","slot":7}</t>
-  </si>
-  <si>
-    <t>Z|n-w-s-e|---|{"packer_id":1,"zone":"order","slot":6}</t>
-  </si>
-  <si>
-    <t>Z|n-w-s-e|---|{"packer_id":1,"zone":"order","slot":5}</t>
-  </si>
-  <si>
-    <t>Z|n-w-s-e|---|{"packer_id":1,"zone":"order","slot":4}</t>
-  </si>
-  <si>
-    <t>Z|n-w-s-e|---|{"packer_id":1,"zone":"order","slot":3}</t>
-  </si>
-  <si>
-    <t>Z|n-w-s-e|---|{"packer_id":1,"zone":"order","slot":2}</t>
-  </si>
-  <si>
-    <t>Z|n-w-s-e|---|{"packer_id":1,"zone":"order","slot":1}</t>
-  </si>
-  <si>
-    <t>Z|n-w-s-e|---|{"packer_id":2,"zone":"order","slot":1}</t>
-  </si>
-  <si>
-    <t>Z|n-w-s-e|---|{"packer_id":2,"zone":"order","slot":2}</t>
-  </si>
-  <si>
-    <t>Z|n-w-s-e|---|{"packer_id":2,"zone":"order","slot":3}</t>
-  </si>
-  <si>
-    <t>Z|n-w-s-e|---|{"packer_id":2,"zone":"order","slot":4}</t>
-  </si>
-  <si>
-    <t>Z|n-w-s-e|---|{"packer_id":2,"zone":"order","slot":5}</t>
-  </si>
-  <si>
-    <t>Z|n-w-s-e|---|{"packer_id":2,"zone":"order","slot":6}</t>
-  </si>
-  <si>
-    <t>Z|n-w-s-e|---|{"packer_id":2,"zone":"order","slot":7}</t>
-  </si>
-  <si>
-    <t>Z|n-w-s-e|---|{"packer_id":2,"zone":"order","slot":8}</t>
-  </si>
-  <si>
-    <t>Z|n-w-s-e|---|{"packer_id":2,"zone":"order","slot":9}</t>
-  </si>
-  <si>
-    <t>Z|n-w-s-e|---|{"packer_id":2,"zone":"order","slot":10}</t>
-  </si>
-  <si>
-    <t>C|---|n-w-s-e|{"charger_id":1}</t>
-  </si>
-  <si>
-    <t>C|---|n-w-s-e|{"charger_id":2}</t>
-  </si>
-  <si>
-    <t>C|---|n-w-s-e|{"charger_id":3}</t>
-  </si>
-  <si>
-    <t>C|---|n-w-s-e|{"charger_id":4}</t>
-  </si>
-  <si>
-    <t>C|---|n-w-s-e|{"charger_id":5}</t>
-  </si>
-  <si>
-    <t>C|---|n-w-s-e|{"charger_id":6}</t>
-  </si>
-  <si>
-    <t>C|---|n-w-s-e|{"charger_id":7}</t>
-  </si>
-  <si>
-    <t>C|---|n-w-s-e|{"charger_id":8}</t>
-  </si>
-  <si>
-    <t>C|---|n-w-s-e|{"charger_id":9}</t>
-  </si>
-  <si>
-    <t>C|---|n-w-s-e|{"charger_id":10}</t>
-  </si>
-  <si>
-    <t>F|n-w-s-e|n-w-s-e|{}</t>
-  </si>
-  <si>
-    <t>F|-w-s-e|-w-s-e|{}</t>
-  </si>
-  <si>
-    <t>F|n-w--e|n-w--e|{}</t>
-  </si>
-  <si>
-    <t>F|n--s-e|n--s-e|{}</t>
-  </si>
-  <si>
-    <t>F|n---e|n---e|{}</t>
-  </si>
-  <si>
-    <t>F|--s-|-w-s-e|{}</t>
-  </si>
-  <si>
-    <t>F|n---|-w-s-e|{}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":0}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":99}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":108}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":117}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":126}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":135}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":144}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":153}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":162}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":171}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":180}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":100}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":109}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":118}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":127}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":136}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":145}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":154}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":163}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":172}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":181}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":101}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":110}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":119}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":128}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":137}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":146}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":155}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":164}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":173}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":182}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":102}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":111}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":120}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":129}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":138}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":147}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":156}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":165}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":174}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":183}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":103}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":112}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":121}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":130}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":139}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":148}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":157}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":166}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":175}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":184}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":104}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":113}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":122}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":131}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":140}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":149}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":158}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":167}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":176}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":185}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":105}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":114}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":123}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":132}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":141}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":150}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":159}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":168}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":177}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":186}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":106}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":115}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":124}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":133}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":142}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":151}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":160}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":169}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":178}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":187}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":107}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":116}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":125}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":134}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":143}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":152}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":161}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":170}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":179}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":188}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":9}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":18}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":27}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":36}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":45}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":54}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":63}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":72}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":81}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":90}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":1}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":10}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":19}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":28}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":37}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":46}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":55}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":64}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":73}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":82}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":91}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":2}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":11}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":20}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":29}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":38}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":47}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":56}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":65}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":74}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":83}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":92}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":3}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":12}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":21}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":30}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":39}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":48}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":57}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":66}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":75}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":84}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":93}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":4}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":13}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":22}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":31}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":40}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":49}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":58}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":67}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":76}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":85}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":94}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":5}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":14}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":23}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":32}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":41}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":50}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":59}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":68}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":77}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":86}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":95}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":6}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":15}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":24}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":33}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":42}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":51}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":60}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":69}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":78}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":87}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":96}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":7}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":16}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":25}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":34}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":43}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":52}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":61}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":70}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":79}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":88}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":97}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":8}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":17}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":26}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":35}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":44}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":53}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":62}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":71}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":80}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":89}</t>
-  </si>
-  <si>
-    <t>S|-w--e|n-w-s-e|{"shelf_id":98}</t>
-  </si>
-  <si>
-    <t>вниз</t>
-  </si>
-  <si>
-    <t>вверх</t>
-  </si>
-  <si>
-    <t>F|n---|n-w--e|{}</t>
-  </si>
-  <si>
-    <t>F|n--s-e|n-w-s-e|{}</t>
-  </si>
-  <si>
-    <t>B|n-w-s-e|n-w-s-e|{"packer_id":1,"zone":"buffer","slot":11}</t>
-  </si>
-  <si>
-    <t>B|n-w-s-e|n-w-s-e|{"packer_id":1,"zone":"buffer","slot":12}</t>
-  </si>
-  <si>
-    <t>B|n-w-s-e|n-w-s-e|{"packer_id":1,"zone":"buffer","slot":13}</t>
-  </si>
-  <si>
-    <t>B|n-w-s-e|n-w-s-e|{"packer_id":1,"zone":"buffer","slot":14}</t>
-  </si>
-  <si>
-    <t>B|n-w-s-e|n-w-s-e|{"packer_id":1,"zone":"buffer","slot":15}</t>
-  </si>
-  <si>
-    <t>B|n-w-s-e|n-w-s-e|{"packer_id":1,"zone":"buffer","slot":16}</t>
-  </si>
-  <si>
-    <t>B|n-w-s-e|n-w-s-e|{"packer_id":1,"zone":"buffer","slot":17}</t>
-  </si>
-  <si>
-    <t>B|n-w-s-e|n-w-s-e|{"packer_id":1,"zone":"buffer","slot":18}</t>
-  </si>
-  <si>
-    <t>B|n-w-s-e|n-w-s-e|{"packer_id":1,"zone":"buffer","slot":19}</t>
-  </si>
-  <si>
-    <t>B|n-w-s-e|n-w-s-e|{"packer_id":1,"zone":"buffer","slot":20}</t>
-  </si>
-  <si>
-    <t>B|n-w-s-e|n-w-s-e|{"packer_id":2,"zone":"buffer","slot":20}</t>
-  </si>
-  <si>
-    <t>B|n-w-s-e|n-w-s-e|{"packer_id":2,"zone":"buffer","slot":19}</t>
-  </si>
-  <si>
-    <t>B|n-w-s-e|n-w-s-e|{"packer_id":2,"zone":"buffer","slot":18}</t>
-  </si>
-  <si>
-    <t>B|n-w-s-e|n-w-s-e|{"packer_id":2,"zone":"buffer","slot":17}</t>
-  </si>
-  <si>
-    <t>B|n-w-s-e|n-w-s-e|{"packer_id":2,"zone":"buffer","slot":16}</t>
-  </si>
-  <si>
-    <t>B|n-w-s-e|n-w-s-e|{"packer_id":2,"zone":"buffer","slot":15}</t>
-  </si>
-  <si>
-    <t>B|n-w-s-e|n-w-s-e|{"packer_id":2,"zone":"buffer","slot":14}</t>
-  </si>
-  <si>
-    <t>B|n-w-s-e|n-w-s-e|{"packer_id":2,"zone":"buffer","slot":13}</t>
-  </si>
-  <si>
-    <t>B|n-w-s-e|n-w-s-e|{"packer_id":2,"zone":"buffer","slot":12}</t>
-  </si>
-  <si>
-    <t>B|n-w-s-e|n-w-s-e|{"packer_id":2,"zone":"buffer","slot":11}</t>
-  </si>
-  <si>
-    <t>E|---|---|{}</t>
-  </si>
-  <si>
-    <t>W|---|---|{}</t>
   </si>
 </sst>
 </file>
@@ -835,7 +772,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -862,12 +799,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0000FF"/>
-        <bgColor rgb="FF0000FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF980000"/>
         <bgColor rgb="FF980000"/>
       </patternFill>
@@ -886,19 +817,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF7030A0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FFFF9900"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -915,32 +840,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF9900"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1157,7 +1085,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AM31"/>
+  <dimension ref="A1:AM32"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="2" customWidth="1"/>
@@ -1171,1034 +1099,1070 @@
   <sheetData>
     <row r="1" spans="1:39" ht="12.75">
       <c r="A1" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC1" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:39" ht="12.75">
       <c r="A2" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="Y2" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="Z2" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:39" ht="12.75">
       <c r="A3" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="R3" s="7" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="S3" s="7" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="T3" s="7" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="U3" s="7" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="V3" s="7" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="W3" s="7" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="X3" s="7" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="Y3" s="7" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="Z3" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC3" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:39" ht="12.75">
       <c r="A4" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>39</v>
+        <v>21</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>28</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="R4" s="5" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="S4" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="T4" s="5" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="U4" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="V4" s="5" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="W4" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="X4" s="5" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="Y4" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Z4" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA4" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC4" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:39" ht="12.75">
       <c r="A5" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="R5" s="5" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="S5" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="T5" s="5" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="U5" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="V5" s="5" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="W5" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="X5" s="5" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="Y5" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Z5" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA5" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC5" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:39" ht="12.75">
       <c r="A6" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="S6" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="U6" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="V6" s="5" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="W6" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="X6" s="5" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="Y6" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Z6" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA6" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC6" s="2">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:39" ht="12.75">
       <c r="A7" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="R7" s="5" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="S7" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="T7" s="5" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="U7" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="V7" s="5" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="W7" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="X7" s="5" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="Y7" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Z7" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA7" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC7" s="2">
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:39" ht="12.75">
       <c r="A8" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="O8" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="P8" s="5" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="R8" s="5" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="S8" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="T8" s="5" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="U8" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="V8" s="5" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="W8" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="X8" s="5" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="Y8" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Z8" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA8" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC8" s="2">
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:39" ht="12.75">
       <c r="A9" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="O9" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="R9" s="5" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="S9" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="T9" s="5" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="U9" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="V9" s="5" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="W9" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="X9" s="5" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="Y9" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Z9" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA9" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AB9" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC9" s="2">
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:39" ht="12.75">
       <c r="A10" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="R10" s="5" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="S10" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="T10" s="5" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="U10" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="V10" s="5" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="W10" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="X10" s="5" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="Y10" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Z10" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA10" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AB10" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC10" s="2">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:39" ht="12.75">
       <c r="A11" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="R11" s="5" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="S11" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="T11" s="5" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="U11" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="V11" s="5" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="W11" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="X11" s="5" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA11" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AB11" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC11" s="2">
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:39" ht="12.75">
       <c r="A12" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="P12" s="5" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="R12" s="5" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="S12" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="T12" s="5" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="U12" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="V12" s="5" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="W12" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="X12" s="5" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="Y12" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Z12" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA12" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AB12" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC12" s="2">
+        <v>12</v>
       </c>
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
@@ -2211,88 +2175,91 @@
     </row>
     <row r="13" spans="1:39" ht="12.75">
       <c r="A13" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L13" s="17" t="s">
-        <v>32</v>
+        <v>21</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>21</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="R13" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="S13" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="T13" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="U13" s="7" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="V13" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="W13" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="X13" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="Y13" s="7" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="Z13" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA13" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AB13" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC13" s="2">
+        <v>13</v>
       </c>
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
@@ -2301,88 +2268,91 @@
     </row>
     <row r="14" spans="1:39" ht="12.75">
       <c r="A14" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="O14" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="P14" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="R14" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="S14" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="T14" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="U14" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="V14" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="W14" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="X14" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="Y14" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="Z14" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA14" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AB14" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC14" s="2">
+        <v>14</v>
       </c>
       <c r="AD14" s="8"/>
       <c r="AE14" s="4"/>
@@ -2391,264 +2361,273 @@
     </row>
     <row r="15" spans="1:39" ht="12.75">
       <c r="A15" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="R15" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="S15" s="7" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="T15" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="U15" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="V15" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="W15" s="7" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="X15" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="Y15" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="Z15" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA15" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AB15" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC15" s="2">
+        <v>15</v>
       </c>
       <c r="AL15" s="9"/>
       <c r="AM15" s="9"/>
     </row>
     <row r="16" spans="1:39" ht="12.75">
       <c r="A16" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>231</v>
+        <v>222</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>29</v>
       </c>
       <c r="E16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I16" s="7" t="s">
+      <c r="K16" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="N16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="O16" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="P16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="R16" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="S16" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="T16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J16" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="L16" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="M16" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="N16" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="O16" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="P16" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q16" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="R16" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="S16" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="T16" s="5" t="s">
-        <v>47</v>
-      </c>
       <c r="U16" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="V16" s="5" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="W16" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="X16" s="5" t="s">
-        <v>49</v>
+        <v>223</v>
       </c>
       <c r="Y16" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Z16" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA16" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AB16" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC16" s="2">
+        <v>16</v>
       </c>
       <c r="AL16" s="9"/>
       <c r="AM16" s="9"/>
     </row>
     <row r="17" spans="1:39" ht="12.75">
       <c r="A17" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C17" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>231</v>
+      <c r="D17" s="16" t="s">
+        <v>39</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="P17" s="5" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="R17" s="5" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="S17" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="T17" s="5" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="U17" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="V17" s="5" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="W17" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="X17" s="5" t="s">
-        <v>59</v>
+        <v>224</v>
       </c>
       <c r="Y17" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Z17" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA17" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AB17" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC17" s="2">
+        <v>17</v>
       </c>
       <c r="AF17" s="4"/>
       <c r="AG17" s="4"/>
@@ -2661,1209 +2640,1337 @@
     </row>
     <row r="18" spans="1:39" ht="12.75">
       <c r="A18" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>231</v>
+        <v>222</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N18" s="5" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="O18" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="P18" s="5" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="R18" s="5" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="S18" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="T18" s="5" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="U18" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="V18" s="5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="W18" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="X18" s="5" t="s">
-        <v>69</v>
+        <v>225</v>
       </c>
       <c r="Y18" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Z18" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA18" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AB18" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC18" s="2">
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:39" ht="12.75">
       <c r="A19" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>231</v>
+        <v>222</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>59</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="P19" s="5" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="R19" s="5" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="S19" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="T19" s="5" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="U19" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="V19" s="5" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="W19" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="X19" s="5" t="s">
-        <v>79</v>
+        <v>226</v>
       </c>
       <c r="Y19" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Z19" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA19" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AB19" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC19" s="2">
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:39" ht="12.75">
       <c r="A20" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>231</v>
+        <v>222</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>69</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="M20" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N20" s="5" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="O20" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="P20" s="5" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="R20" s="5" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="S20" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="T20" s="5" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="U20" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="V20" s="5" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="W20" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="X20" s="5" t="s">
-        <v>89</v>
+        <v>227</v>
       </c>
       <c r="Y20" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Z20" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA20" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AB20" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC20" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:39" ht="12.75">
       <c r="A21" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>231</v>
+        <v>222</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>79</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N21" s="5" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="P21" s="5" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="R21" s="5" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="S21" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="T21" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="U21" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="V21" s="5" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="W21" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="X21" s="5" t="s">
-        <v>99</v>
+        <v>228</v>
       </c>
       <c r="Y21" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Z21" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA21" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AB21" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC21" s="2">
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:39" ht="12.75">
       <c r="A22" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>231</v>
+        <v>222</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>89</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="N22" s="5" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="P22" s="5" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="R22" s="5" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="S22" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="T22" s="5" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="U22" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="V22" s="5" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="W22" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="X22" s="5" t="s">
-        <v>109</v>
+        <v>229</v>
       </c>
       <c r="Y22" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Z22" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA22" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AB22" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC22" s="2">
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:39" ht="12.75">
       <c r="A23" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>231</v>
+        <v>222</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>99</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="G23" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="N23" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="O23" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="P23" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q23" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="R23" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="S23" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="T23" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="U23" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="V23" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="W23" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="X23" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="H23" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="L23" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="M23" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="N23" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="O23" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="P23" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q23" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="R23" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="S23" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="T23" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="U23" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="V23" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="W23" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="X23" s="5" t="s">
-        <v>119</v>
-      </c>
       <c r="Y23" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Z23" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA23" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AB23" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC23" s="2">
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:39" ht="12.75">
       <c r="A24" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D24" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="N24" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="O24" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="P24" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q24" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="R24" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="S24" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="T24" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="U24" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="V24" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="W24" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="X24" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="K24" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="L24" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="M24" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="N24" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="O24" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="P24" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q24" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="R24" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="S24" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="T24" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="U24" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="V24" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="W24" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="X24" s="5" t="s">
-        <v>129</v>
-      </c>
       <c r="Y24" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Z24" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA24" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AB24" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC24" s="2">
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:39" ht="12.75">
       <c r="A25" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>31</v>
+        <v>222</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="P25" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="Q25" s="7" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="R25" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="S25" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="T25" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="U25" s="7" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="V25" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="W25" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="X25" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="Y25" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="Z25" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA25" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AB25" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC25" s="2">
+        <v>25</v>
       </c>
       <c r="AD25" s="4"/>
     </row>
     <row r="26" spans="1:39" ht="12.75">
       <c r="A26" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="N26" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="O26" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="P26" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="Q26" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="R26" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="S26" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="T26" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="U26" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="V26" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="W26" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="X26" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="Y26" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="Z26" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA26" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AB26" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC26" s="2">
+        <v>26</v>
       </c>
       <c r="AD26" s="4"/>
     </row>
     <row r="27" spans="1:39" ht="12.75">
       <c r="A27" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="G27" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="H27" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="I27" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="J27" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="K27" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="L27" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="M27" s="12" t="s">
-        <v>241</v>
+        <v>21</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="N27" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="O27" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="P27" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q27" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="R27" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="S27" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="T27" s="12" t="s">
-        <v>246</v>
-      </c>
-      <c r="U27" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="V27" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="W27" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="X27" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="Y27" s="12" t="s">
-        <v>251</v>
+        <v>21</v>
+      </c>
+      <c r="P27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="R27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="S27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="T27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="U27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="V27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="W27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="X27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y27" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="Z27" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA27" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AB27" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC27" s="2">
+        <v>27</v>
       </c>
       <c r="AD27" s="4"/>
     </row>
     <row r="28" spans="1:39" ht="12.75">
       <c r="A28" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="M28" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="N28" s="7" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="O28" s="7" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="P28" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="Q28" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="R28" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="S28" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="T28" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="U28" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="V28" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="W28" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="X28" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="Y28" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="Z28" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA28" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AB28" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC28" s="2">
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:39" ht="15.75" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D29" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E29" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="F29" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="G29" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G29" s="14" t="s">
+      <c r="H29" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="H29" s="14" t="s">
+      <c r="I29" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="I29" s="14" t="s">
+      <c r="J29" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="J29" s="14" t="s">
+      <c r="K29" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="K29" s="14" t="s">
+      <c r="L29" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="L29" s="14" t="s">
+      <c r="M29" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="M29" s="14" t="s">
+      <c r="N29" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="O29" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="P29" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="N29" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="O29" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="P29" s="13" t="s">
+      <c r="Q29" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="Q29" s="13" t="s">
+      <c r="R29" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="R29" s="13" t="s">
+      <c r="S29" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="S29" s="13" t="s">
+      <c r="T29" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="T29" s="13" t="s">
+      <c r="U29" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="U29" s="13" t="s">
+      <c r="V29" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="V29" s="13" t="s">
+      <c r="W29" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="W29" s="13" t="s">
+      <c r="X29" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="X29" s="13" t="s">
+      <c r="Y29" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="Y29" s="13" t="s">
-        <v>21</v>
-      </c>
       <c r="Z29" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AA29" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AB29" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC29" s="2">
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:39" ht="15.75" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="M30" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="M30" s="10" t="s">
         <v>0</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="P30" s="11" t="s">
-        <v>1</v>
+        <v>222</v>
+      </c>
+      <c r="P30" s="10" t="s">
+        <v>232</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="T30" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="U30" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="V30" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="W30" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="X30" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="Y30" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="Z30" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AA30" s="3" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="AB30" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC30" s="2">
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:39" ht="15.75" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="V31" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="X31" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="Y31" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="Z31" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="AA31" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="AB31" s="1" t="s">
-        <v>252</v>
+        <v>221</v>
+      </c>
+      <c r="AC31" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:39" ht="15.75" customHeight="1">
+      <c r="A32" s="2">
+        <v>1</v>
+      </c>
+      <c r="B32" s="2">
+        <v>2</v>
+      </c>
+      <c r="C32" s="2">
+        <v>3</v>
+      </c>
+      <c r="D32" s="2">
+        <v>4</v>
+      </c>
+      <c r="E32" s="2">
+        <v>5</v>
+      </c>
+      <c r="F32" s="2">
+        <v>6</v>
+      </c>
+      <c r="G32" s="2">
+        <v>7</v>
+      </c>
+      <c r="H32" s="2">
+        <v>8</v>
+      </c>
+      <c r="I32" s="2">
+        <v>9</v>
+      </c>
+      <c r="J32" s="2">
+        <v>10</v>
+      </c>
+      <c r="K32" s="2">
+        <v>11</v>
+      </c>
+      <c r="L32" s="2">
+        <v>12</v>
+      </c>
+      <c r="M32" s="2">
+        <v>13</v>
+      </c>
+      <c r="N32" s="2">
+        <v>14</v>
+      </c>
+      <c r="O32" s="2">
+        <v>15</v>
+      </c>
+      <c r="P32" s="2">
+        <v>16</v>
+      </c>
+      <c r="Q32" s="2">
+        <v>17</v>
+      </c>
+      <c r="R32" s="2">
+        <v>18</v>
+      </c>
+      <c r="S32" s="2">
+        <v>19</v>
+      </c>
+      <c r="T32" s="2">
+        <v>20</v>
+      </c>
+      <c r="U32" s="2">
+        <v>21</v>
+      </c>
+      <c r="V32" s="2">
+        <v>22</v>
+      </c>
+      <c r="W32" s="2">
+        <v>23</v>
+      </c>
+      <c r="X32" s="2">
+        <v>24</v>
+      </c>
+      <c r="Y32" s="2">
+        <v>25</v>
+      </c>
+      <c r="Z32" s="2">
+        <v>26</v>
+      </c>
+      <c r="AA32" s="2">
+        <v>27</v>
+      </c>
+      <c r="AB32" s="2">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -3878,83 +3985,83 @@
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>229</v>
+      <c r="A1" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/maps/map1.xlsx
+++ b/maps/map1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\projects in programming\python\AgentStorage\AgentStorageDiplom\maps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{046C11BC-2F5C-437B-B889-BB6256504238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A8E3B3-A036-4664-AAB5-2AE6E3C23BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
